--- a/results/spearman_results.xlsx
+++ b/results/spearman_results.xlsx
@@ -7433,13 +7433,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1576BEB7-EB62-4462-ABB8-CC6D76ED0CD7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F11B281B-3FA4-475F-B792-FF4C6393475B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC15800-8B2D-4D8A-B80E-C19F223352D9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB64BFBD-5EDF-40F1-A672-72AD28D195FE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B664C70-5C7F-4CF0-A087-B253D6E123B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7679EED1-B566-4330-8F57-28A1FC3C5431}"/>
 </file>
--- a/results/spearman_results.xlsx
+++ b/results/spearman_results.xlsx
@@ -7433,13 +7433,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F11B281B-3FA4-475F-B792-FF4C6393475B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70779224-801B-4939-B835-4BBAF3B16A50}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB64BFBD-5EDF-40F1-A672-72AD28D195FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{07D737B8-483B-43B8-AEB1-0BB891D0DB58}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7679EED1-B566-4330-8F57-28A1FC3C5431}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99D0D45B-11D5-4B52-80CC-2D6C2CB8D2D4}"/>
 </file>